--- a/data-source/盾牌数据.xlsx
+++ b/data-source/盾牌数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2326D82F-637D-4248-8F21-04EFE1494D7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1B8847-CE19-4BF0-BA2C-4FC6CAAEE34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -172,18 +172,6 @@
     <t>原松木：3；亚麻纤维：2；绳子：1</t>
   </si>
   <si>
-    <t>铜锭：2；松木板：5；粗绳：6；皮革：3；绳子：3</t>
-  </si>
-  <si>
-    <t>青铜锭：2；青铜钉：2；松木板：7；粗绳：5；皮革：6</t>
-  </si>
-  <si>
-    <t>铁锭：8；青铜钉：5；桦木板：6；粗绳：8；皮革：12</t>
-  </si>
-  <si>
-    <t>铁锭：10；青铜钉：8；桦木板：6；线：8；粗绳：12</t>
-  </si>
-  <si>
     <t>小圆盾</t>
   </si>
   <si>
@@ -209,6 +197,18 @@
   </si>
   <si>
     <t>碎铜片：1；原松木：5；皮革：2；绳子：3</t>
+  </si>
+  <si>
+    <t>铜锭：2；松木板：5；皮条：6；皮革：3；绳子：3</t>
+  </si>
+  <si>
+    <t>青铜锭：2；青铜钉：2；松木板：7；皮条：5；皮革：6</t>
+  </si>
+  <si>
+    <t>铁锭：8；青铜钉：5；桦木板：6；皮条：8；皮革：12</t>
+  </si>
+  <si>
+    <t>铁锭：10；青铜钉：8；桦木板：6；线：8；皮条：12</t>
   </si>
 </sst>
 </file>
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -691,7 +691,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C2" s="5">
         <v>6</v>
@@ -711,13 +711,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C3" s="5">
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
@@ -731,13 +731,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C4" s="5">
         <v>22</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>10</v>
@@ -751,13 +751,13 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C5" s="5">
         <v>27</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>12</v>
@@ -771,13 +771,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C6" s="5">
         <v>50</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>14</v>
@@ -791,7 +791,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C7" s="5">
         <v>50</v>
@@ -806,16 +806,16 @@
     </row>
     <row r="8" spans="1:6" ht="35.25" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>56</v>
       </c>
       <c r="C8" s="5">
         <v>70</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>19</v>
@@ -829,7 +829,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" s="5">
         <v>20</v>
@@ -847,7 +847,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" s="5">
         <v>100</v>
@@ -865,7 +865,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C11" s="5">
         <v>115</v>
@@ -883,7 +883,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12" s="5">
         <v>150</v>
@@ -901,7 +901,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C13" s="5">
         <v>150</v>
@@ -919,7 +919,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" s="5">
         <v>150</v>
@@ -937,7 +937,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C15" s="5">
         <v>200</v>
@@ -955,7 +955,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C16" s="5">
         <v>150</v>
@@ -973,7 +973,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C17" s="5">
         <v>150</v>
@@ -991,7 +991,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C18" s="5">
         <v>150</v>

--- a/data-source/盾牌数据.xlsx
+++ b/data-source/盾牌数据.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E1B8847-CE19-4BF0-BA2C-4FC6CAAEE34D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A6D76A-D9D6-4B45-88FE-19406E6EE1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
   <si>
     <t>护盾数据</t>
   </si>
@@ -173,9 +173,6 @@
   </si>
   <si>
     <t>小圆盾</t>
-  </si>
-  <si>
-    <t>待测</t>
   </si>
   <si>
     <t>耐久</t>
@@ -671,7 +668,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
@@ -691,7 +688,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C2" s="5">
         <v>6</v>
@@ -711,13 +708,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="5">
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
@@ -731,13 +728,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" s="5">
         <v>22</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>10</v>
@@ -751,13 +748,13 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" s="5">
         <v>27</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>12</v>
@@ -771,13 +768,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6" s="5">
         <v>50</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>14</v>
@@ -791,7 +788,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C7" s="5">
         <v>50</v>
@@ -809,13 +806,13 @@
         <v>48</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C8" s="5">
         <v>70</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>19</v>
@@ -829,7 +826,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" s="5">
         <v>20</v>
@@ -847,7 +844,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="5">
         <v>100</v>
@@ -865,7 +862,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5">
         <v>115</v>
@@ -883,7 +880,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C12" s="5">
         <v>150</v>
@@ -901,7 +898,7 @@
         <v>32</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C13" s="5">
         <v>150</v>
@@ -919,7 +916,7 @@
         <v>35</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="5">
         <v>150</v>
@@ -937,7 +934,7 @@
         <v>37</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="5">
         <v>200</v>
@@ -955,7 +952,7 @@
         <v>39</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="5">
         <v>150</v>
@@ -973,7 +970,7 @@
         <v>41</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="5">
         <v>150</v>
@@ -991,7 +988,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" s="5">
         <v>150</v>

--- a/data-source/盾牌数据.xlsx
+++ b/data-source/盾牌数据.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Grimsoul-WIKI\grimsoul-wiki\data-source\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6A6D76A-D9D6-4B45-88FE-19406E6EE1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22982338-C393-4682-A4B0-CD0ED973260B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
   <si>
     <t>护盾数据</t>
   </si>
@@ -97,9 +97,6 @@
 抵挡伤害减少20-40点，自身生命值越低，可抵挡的伤害越高</t>
   </si>
   <si>
-    <t>英雄大车炮台</t>
-  </si>
-  <si>
     <t>眩晕盾</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>铁锭：10；青铜钉：8；桦木板：6；线：8；皮条：12</t>
+  </si>
+  <si>
+    <t>红猎图纸</t>
   </si>
 </sst>
 </file>
@@ -668,13 +668,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -688,13 +688,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="5">
         <v>6</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>5</v>
@@ -708,13 +708,13 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C3" s="5">
         <v>17</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>8</v>
@@ -728,13 +728,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" s="5">
         <v>22</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>10</v>
@@ -748,13 +748,13 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" s="5">
         <v>27</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>12</v>
@@ -768,13 +768,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" s="5">
         <v>50</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>14</v>
@@ -788,7 +788,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C7" s="5">
         <v>50</v>
@@ -803,16 +803,16 @@
     </row>
     <row r="8" spans="1:6" ht="35.25" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C8" s="5">
         <v>70</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>19</v>
@@ -826,179 +826,181 @@
         <v>21</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C9" s="5">
         <v>20</v>
       </c>
-      <c r="D9" s="13"/>
+      <c r="D9" s="15" t="s">
+        <v>56</v>
+      </c>
       <c r="E9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="32.25" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="5">
         <v>100</v>
       </c>
       <c r="D10" s="13"/>
       <c r="E10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="35.65" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" s="5">
         <v>115</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="32.65" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="5">
         <v>150</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="27.4" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C13" s="5">
         <v>150</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="29.65" customHeight="1">
       <c r="A14" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C14" s="5">
         <v>150</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="44.25" customHeight="1">
       <c r="A15" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="5">
         <v>200</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="34.5" customHeight="1">
       <c r="A16" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="5">
         <v>150</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="38.25" customHeight="1">
       <c r="A17" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="5">
         <v>150</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="49.9" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C18" s="5">
         <v>150</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>44</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>45</v>
       </c>
     </row>
   </sheetData>
